--- a/Team-Data/2014-15/1-11-2014-15.xlsx
+++ b/Team-Data/2014-15/1-11-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,88 +728,88 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.784</v>
+        <v>0.778</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="K2" t="n">
         <v>0.467</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.383</v>
+        <v>0.378</v>
       </c>
       <c r="O2" t="n">
         <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R2" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S2" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T2" t="n">
         <v>41.3</v>
       </c>
       <c r="U2" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.9</v>
+        <v>102.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -751,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -769,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>11</v>
@@ -784,25 +851,25 @@
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -933,7 +1000,7 @@
         <v>24</v>
       </c>
       <c r="AH3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
         <v>3</v>
@@ -963,19 +1030,19 @@
         <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -987,10 +1054,10 @@
         <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1118,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>24</v>
@@ -1148,22 +1215,22 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
@@ -1303,7 +1370,7 @@
         <v>23</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1318,7 +1385,7 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
@@ -1354,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -1479,10 +1546,10 @@
         <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -1571,64 +1638,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.514</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L7" t="n">
         <v>8.1</v>
       </c>
       <c r="M7" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="N7" t="n">
         <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S7" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T7" t="n">
         <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V7" t="n">
         <v>13.8</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
@@ -1640,31 +1707,31 @@
         <v>17.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.8</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
@@ -1673,31 +1740,31 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
@@ -1706,19 +1773,19 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -1753,34 +1820,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.703</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.475</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.361</v>
@@ -1789,28 +1856,28 @@
         <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>12.2</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
         <v>5</v>
@@ -1825,31 +1892,31 @@
         <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>2</v>
@@ -1858,28 +1925,28 @@
         <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1900,13 +1967,13 @@
         <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2025,22 +2092,22 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>12</v>
       </c>
       <c r="AM9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN9" t="n">
         <v>26</v>
@@ -2067,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2085,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>19</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
@@ -2225,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>26</v>
@@ -2258,7 +2325,7 @@
         <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>30</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2446,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.694</v>
+        <v>0.703</v>
       </c>
       <c r="H12" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
         <v>0.435</v>
@@ -2508,79 +2575,79 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O12" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="R12" t="n">
         <v>12.4</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>101.3</v>
+        <v>101.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,10 +2659,10 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="AS12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
         <v>22</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>23</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,19 +2686,19 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>22</v>
@@ -2765,7 +2832,7 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
@@ -2783,7 +2850,7 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2792,7 +2859,7 @@
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2801,16 +2868,16 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
         <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.658</v>
+        <v>0.676</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J14" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>10.3</v>
@@ -2875,34 +2942,34 @@
         <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.752</v>
       </c>
       <c r="R14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="U14" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="V14" t="n">
         <v>12.5</v>
       </c>
       <c r="W14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
@@ -2911,25 +2978,25 @@
         <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.4</v>
+        <v>106.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
@@ -2938,10 +3005,10 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2950,13 +3017,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN14" t="n">
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
@@ -2968,22 +3035,22 @@
         <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3042,49 +3109,49 @@
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J15" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>24.6</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.3</v>
       </c>
       <c r="T15" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.7</v>
@@ -3093,19 +3160,19 @@
         <v>4.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.7</v>
+        <v>101.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
@@ -3126,43 +3193,43 @@
         <v>3</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
         <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
         <v>16</v>
@@ -3171,13 +3238,13 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.703</v>
+        <v>0.694</v>
       </c>
       <c r="H16" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J16" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O16" t="n">
         <v>18.1</v>
@@ -3248,61 +3315,61 @@
         <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U16" t="n">
         <v>22.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="W16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
         <v>5.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>101.8</v>
+        <v>101.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
@@ -3317,25 +3384,25 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
@@ -3347,19 +3414,19 @@
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.432</v>
+        <v>0.417</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J17" t="n">
-        <v>74.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M17" t="n">
         <v>20.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O17" t="n">
         <v>18.1</v>
@@ -3430,19 +3497,19 @@
         <v>24.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="T17" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="U17" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="V17" t="n">
         <v>14.4</v>
@@ -3454,7 +3521,7 @@
         <v>3.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z17" t="n">
         <v>20.2</v>
@@ -3463,22 +3530,22 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3502,10 +3569,10 @@
         <v>16</v>
       </c>
       <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
         <v>9</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3724,13 @@
         <v>13</v>
       </c>
       <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
         <v>14</v>
       </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3699,7 +3766,7 @@
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3717,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>16</v>
@@ -3854,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3866,13 +3933,13 @@
         <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,7 +3948,7 @@
         <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -3893,7 +3960,7 @@
         <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,88 +4022,88 @@
         <v>38.8</v>
       </c>
       <c r="J20" t="n">
-        <v>84.3</v>
+        <v>84.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
         <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT20" t="n">
         <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,22 +4139,22 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>6</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BA20" t="n">
         <v>26</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>28</v>
-      </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4266,7 +4333,7 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH22" t="n">
         <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4400,7 +4467,7 @@
         <v>14</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>17</v>
@@ -4430,25 +4497,25 @@
         <v>2</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
         <v>0.368</v>
       </c>
       <c r="O23" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="P23" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
@@ -4576,19 +4643,19 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4606,31 +4673,31 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>18</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4779,13 +4846,13 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J25" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L25" t="n">
         <v>9.9</v>
       </c>
       <c r="M25" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="O25" t="n">
         <v>17.4</v>
@@ -4886,49 +4953,49 @@
         <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U25" t="n">
         <v>20.7</v>
       </c>
       <c r="V25" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -4937,13 +5004,13 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>9</v>
@@ -4955,10 +5022,10 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4970,16 +5037,16 @@
         <v>17</v>
       </c>
       <c r="AS25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT25" t="n">
         <v>17</v>
       </c>
-      <c r="AT25" t="n">
-        <v>16</v>
-      </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
@@ -4991,16 +5058,16 @@
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
       <c r="H26" t="n">
         <v>48.7</v>
@@ -5056,40 +5123,40 @@
         <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O26" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.788</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S26" t="n">
         <v>35.4</v>
       </c>
       <c r="T26" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V26" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
         <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
@@ -5098,16 +5165,16 @@
         <v>19.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>103.8</v>
+        <v>103.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5128,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5149,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,13 +5234,13 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5211,31 +5278,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>21</v>
       </c>
       <c r="G27" t="n">
-        <v>0.432</v>
+        <v>0.417</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
         <v>15.5</v>
@@ -5244,19 +5311,19 @@
         <v>0.344</v>
       </c>
       <c r="O27" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="P27" t="n">
-        <v>30.2</v>
+        <v>30.6</v>
       </c>
       <c r="Q27" t="n">
         <v>0.774</v>
       </c>
       <c r="R27" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T27" t="n">
         <v>44.5</v>
@@ -5265,61 +5332,61 @@
         <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="AB27" t="n">
         <v>102.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
         <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5349,7 +5416,7 @@
         <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.595</v>
+        <v>0.605</v>
       </c>
       <c r="H28" t="n">
         <v>49.2</v>
@@ -5411,43 +5478,43 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.371</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
@@ -5456,10 +5523,10 @@
         <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
         <v>20.5</v>
@@ -5471,7 +5538,7 @@
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5489,13 +5556,13 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
@@ -5504,13 +5571,13 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,31 +5586,31 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
         <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>6.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>7</v>
@@ -5662,10 +5729,10 @@
         <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
@@ -5674,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5695,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS29" t="n">
         <v>25</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>21</v>
@@ -5719,10 +5786,10 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5877,13 +5944,13 @@
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5892,10 +5959,10 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
         <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>0.676</v>
+        <v>0.694</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K31" t="n">
         <v>0.473</v>
@@ -5966,34 +6033,34 @@
         <v>6.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.392</v>
+        <v>0.397</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.737</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S31" t="n">
         <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U31" t="n">
         <v>25</v>
       </c>
       <c r="V31" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.9</v>
@@ -6005,37 +6072,37 @@
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>7</v>
       </c>
       <c r="AF31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AH31" t="n">
         <v>14</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6044,7 +6111,7 @@
         <v>26</v>
       </c>
       <c r="AM31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -6056,13 +6123,13 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6071,28 +6138,28 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
         <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-11-2014-15</t>
+          <t>2015-01-11</t>
         </is>
       </c>
     </row>
